--- a/data/saeop/특화사업.xlsx
+++ b/data/saeop/특화사업.xlsx
@@ -952,7 +952,7 @@
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>교통안전베테랑</v>
+        <v>러브레드봉사단</v>
       </c>
       <c r="E15" t="str">
         <v>설명</v>
@@ -984,7 +984,7 @@
         <v/>
       </c>
       <c r="D16" t="str">
-        <v>교통안전베테랑</v>
+        <v>러브레드봉사단</v>
       </c>
       <c r="E16" t="str">
         <v>정보</v>
@@ -1016,7 +1016,7 @@
         <v/>
       </c>
       <c r="D17" t="str">
-        <v>교통안전베테랑</v>
+        <v>러브레드봉사단</v>
       </c>
       <c r="E17" t="str">
         <v>내용제목</v>
@@ -1048,7 +1048,7 @@
         <v/>
       </c>
       <c r="D18" t="str">
-        <v>교통안전베테랑</v>
+        <v>러브레드봉사단</v>
       </c>
       <c r="E18" t="str">
         <v>내용</v>
